--- a/public/Nutzerstudie/Assets/Results/Analysis_Output/Demografie/00_Demografie_Auswertung.xlsx
+++ b/public/Nutzerstudie/Assets/Results/Analysis_Output/Demografie/00_Demografie_Auswertung.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Übersicht'!$A$1:$C$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alter'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alter'!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Bildungsabschluss'!$A$1:$C$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Vertrautheit'!$A$1:$C$8</definedName>
   </definedNames>
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>13</v>
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>13</v>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.08</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="4">
@@ -581,18 +581,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>50-54</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>60-64</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>2</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>15.38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C6"/>
+  <autoFilter ref="A1:C7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -661,10 +674,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>23.08</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="5">
@@ -687,10 +700,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>15.38</v>
+        <v>23.08</v>
       </c>
     </row>
   </sheetData>
@@ -737,10 +750,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>69.23</v>
+        <v>61.54</v>
       </c>
     </row>
     <row r="3">
@@ -750,10 +763,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.69</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="4">

--- a/public/Nutzerstudie/Assets/Results/Analysis_Output/Demografie/00_Demografie_Auswertung.xlsx
+++ b/public/Nutzerstudie/Assets/Results/Analysis_Output/Demografie/00_Demografie_Auswertung.xlsx
@@ -457,10 +457,10 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" t="n">
         <v>14</v>
-      </c>
-      <c r="C2" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" t="n">
         <v>14</v>
-      </c>
-      <c r="C3" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
         <v>14</v>
-      </c>
-      <c r="C4" t="n">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -536,7 +536,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="3">
@@ -549,7 +549,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="4">
@@ -562,7 +562,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="5">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="6">
@@ -588,7 +588,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="7">
@@ -601,7 +601,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
     </row>
   </sheetData>
@@ -651,7 +651,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="3">
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -677,7 +677,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="5">
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="6">
@@ -703,7 +703,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
     </row>
   </sheetData>
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -766,7 +766,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="4">
@@ -779,7 +779,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="5">
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="7">

--- a/public/Nutzerstudie/Assets/Results/Analysis_Output/Demografie/00_Demografie_Auswertung.xlsx
+++ b/public/Nutzerstudie/Assets/Results/Analysis_Output/Demografie/00_Demografie_Auswertung.xlsx
@@ -457,10 +457,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -533,10 +533,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>21.43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -549,7 +549,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="4">
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>28.57</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="5">
@@ -575,7 +575,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="6">
@@ -588,7 +588,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>7.14</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7">
@@ -601,7 +601,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
     </row>
   </sheetData>
@@ -651,7 +651,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.14</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="3">
@@ -664,7 +664,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="4">
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.29</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="5">
@@ -687,10 +687,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>7.14</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="6">
@@ -703,7 +703,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>21.43</v>
+        <v>18.75</v>
       </c>
     </row>
   </sheetData>
@@ -753,7 +753,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>64.29000000000001</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="3">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>14.29</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="4">
@@ -779,7 +779,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="5">
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="6">
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>7.14</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7">
